--- a/data/pack/ca/avena_pienso_ab.xlsx
+++ b/data/pack/ca/avena_pienso_ab.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4944,6 +4944,61 @@
         </is>
       </c>
       <c r="K82" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>avena_pienso_ab</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Avena forrajera, oferta de elevador (Alberta)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>260</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5047,7 +5102,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5113,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -5153,7 +5208,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
     </row>

--- a/data/pack/ca/avena_pienso_ab.xlsx
+++ b/data/pack/ca/avena_pienso_ab.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4999,6 +4999,61 @@
         </is>
       </c>
       <c r="K83" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>avena_pienso_ab</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Avena forrajera, oferta de elevador (Alberta)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>260.58</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5102,7 +5157,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -5113,7 +5168,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -5208,7 +5263,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>

--- a/data/pack/ca/avena_pienso_ab.xlsx
+++ b/data/pack/ca/avena_pienso_ab.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5054,6 +5054,61 @@
         </is>
       </c>
       <c r="K84" t="inlineStr">
+        <is>
+          <t>Contains information licensed under the Open Government Licence – Alberta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>avena_pienso_ab</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Avena forrajera, oferta de elevador (Alberta)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>260</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Alberta Agriculture and Irrigation — Weekly Market Review</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>OGL-Alberta</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>Contains information licensed under the Open Government Licence – Alberta.</t>
         </is>
@@ -5157,7 +5212,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5223,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
@@ -5263,7 +5318,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
